--- a/data/trans_dic/P1423-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Estudios-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>3,97; 6,75</t>
+          <t>4,03; 6,78</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,25; 8,63</t>
+          <t>5,06; 8,61</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,77; 6,95</t>
+          <t>3,78; 7,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,19; 13,58</t>
+          <t>8,41; 13,27</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 13,07</t>
+          <t>9,71; 13,1</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>17,11; 21,48</t>
+          <t>16,91; 21,29</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,35; 19,31</t>
+          <t>14,57; 19,51</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,61; 22,06</t>
+          <t>17,38; 21,51</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,57; 9,81</t>
+          <t>7,6; 9,92</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,56; 15,5</t>
+          <t>12,58; 15,68</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,29; 13,6</t>
+          <t>10,33; 13,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,28; 17,9</t>
+          <t>14,2; 17,49</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,32; 2,63</t>
+          <t>1,25; 2,58</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,29; 4,04</t>
+          <t>2,3; 4,11</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,21; 3,74</t>
+          <t>2,17; 3,71</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,29; 5,82</t>
+          <t>3,18; 5,86</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,51; 6,79</t>
+          <t>4,39; 6,73</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,14; 8,79</t>
+          <t>6,12; 8,78</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,54; 10,12</t>
+          <t>7,42; 10,04</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>6,97; 11,44</t>
+          <t>7,25; 11,31</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,05; 4,33</t>
+          <t>3,0; 4,32</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,43; 5,96</t>
+          <t>4,39; 5,95</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,02; 6,56</t>
+          <t>5,01; 6,52</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,63; 8,26</t>
+          <t>5,86; 8,27</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,56; 4,3</t>
+          <t>1,53; 4,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,47; 4,96</t>
+          <t>1,4; 4,82</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,9; 3,59</t>
+          <t>0,88; 3,47</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,59; 7,59</t>
+          <t>3,53; 7,53</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,72; 6,75</t>
+          <t>2,75; 6,51</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,13</t>
+          <t>2,3; 6,26</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,93; 5,51</t>
+          <t>1,82; 5,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,64; 9,23</t>
+          <t>5,58; 9,29</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,53; 4,88</t>
+          <t>2,41; 4,75</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,24; 4,84</t>
+          <t>2,2; 4,65</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,57; 3,86</t>
+          <t>1,72; 3,81</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>4,95; 7,64</t>
+          <t>5,0; 7,72</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,7</t>
+          <t>2,52; 3,74</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,44; 4,92</t>
+          <t>3,47; 4,89</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,77; 3,98</t>
+          <t>2,72; 3,9</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,5; 6,72</t>
+          <t>4,3; 6,63</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,71; 8,54</t>
+          <t>6,72; 8,53</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,33; 12,56</t>
+          <t>10,35; 12,52</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,12; 11,19</t>
+          <t>9,08; 11,23</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,2; 12,48</t>
+          <t>9,22; 12,49</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,88; 5,99</t>
+          <t>4,91; 5,96</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,07; 8,43</t>
+          <t>7,16; 8,51</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,15; 7,44</t>
+          <t>6,22; 7,52</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,47; 9,39</t>
+          <t>7,43; 9,48</t>
         </is>
       </c>
     </row>
@@ -1246,7 +1246,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad)</t>
+          <t>Población con enfermedades crónicas de salud mental (trastornos depresivos o ansiedad) (tasa de respuesta: 99,99%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>40920; 69683</t>
+          <t>41532; 69900</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>51148; 84077</t>
+          <t>49272; 83884</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28432; 52435</t>
+          <t>28516; 53274</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42188; 69917</t>
+          <t>43304; 68342</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>126173; 171886</t>
+          <t>127684; 172285</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>228900; 287334</t>
+          <t>226155; 284830</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>142720; 192020</t>
+          <t>144902; 194098</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>133076; 166703</t>
+          <t>131296; 162542</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>177623; 230193</t>
+          <t>178263; 232728</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>290469; 358484</t>
+          <t>290928; 362647</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>179946; 237885</t>
+          <t>180667; 236105</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>181381; 227436</t>
+          <t>180388; 222192</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>22404; 44544</t>
+          <t>21222; 43688</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>44934; 79281</t>
+          <t>45181; 80643</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45812; 77641</t>
+          <t>45005; 76946</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>75329; 133222</t>
+          <t>72752; 134134</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>71616; 107815</t>
+          <t>69719; 106828</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>107662; 154173</t>
+          <t>107364; 154026</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>149963; 201262</t>
+          <t>147513; 199711</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>155914; 255903</t>
+          <t>162228; 253074</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>99978; 141926</t>
+          <t>98436; 141785</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>164747; 221717</t>
+          <t>163197; 221172</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>204148; 266573</t>
+          <t>203621; 265070</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>255035; 373844</t>
+          <t>265300; 374527</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8606; 23713</t>
+          <t>8446; 23222</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>7052; 23861</t>
+          <t>6757; 23213</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4932; 19652</t>
+          <t>4818; 18972</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>23228; 49101</t>
+          <t>22858; 48705</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>12970; 32138</t>
+          <t>13087; 30996</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10567; 28104</t>
+          <t>10562; 28717</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>10614; 30242</t>
+          <t>9986; 27992</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>37278; 60948</t>
+          <t>36855; 61352</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>25981; 50121</t>
+          <t>24763; 48784</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>21021; 45464</t>
+          <t>20710; 43656</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>17211; 42284</t>
+          <t>18859; 41711</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>64723; 99886</t>
+          <t>65290; 100892</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82495; 121211</t>
+          <t>82672; 122507</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>117782; 168339</t>
+          <t>118636; 167214</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>93706; 134446</t>
+          <t>91881; 131811</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>155327; 232009</t>
+          <t>148591; 229004</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>226831; 288464</t>
+          <t>226997; 288276</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>366737; 445972</t>
+          <t>367564; 444633</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>322072; 395353</t>
+          <t>320816; 396560</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>336075; 455830</t>
+          <t>336824; 456287</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>324573; 398476</t>
+          <t>326547; 396959</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>492572; 587593</t>
+          <t>499446; 593168</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>424927; 514353</t>
+          <t>430016; 519891</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>530864; 667536</t>
+          <t>528253; 673333</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P1423-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P1423-Estudios-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>9,87%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>19,89%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>15,9%</t>
+          <t>15,75%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>4,03; 6,78</t>
+          <t>4,03; 6,85</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>5,06; 8,61</t>
+          <t>5,23; 8,68</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>3,78; 7,06</t>
+          <t>3,88; 7,06</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8,41; 13,27</t>
+          <t>7,75; 12,23</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 13,1</t>
+          <t>9,6; 13,0</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>16,91; 21,29</t>
+          <t>17,11; 21,58</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,57; 19,51</t>
+          <t>14,55; 19,28</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>17,38; 21,51</t>
+          <t>17,77; 21,95</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>7,6; 9,92</t>
+          <t>7,6; 9,91</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>12,58; 15,68</t>
+          <t>12,6; 15,63</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10,33; 13,5</t>
+          <t>10,34; 13,53</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,2; 17,49</t>
+          <t>14,03; 17,39</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4,76%</t>
+          <t>5,39%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>9,74%</t>
+          <t>11,03%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>7,22%</t>
+          <t>8,17%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>1,25; 2,58</t>
+          <t>1,31; 2,59</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,3; 4,11</t>
+          <t>2,28; 4,04</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,17; 3,71</t>
+          <t>2,24; 3,74</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>3,18; 5,86</t>
+          <t>4,5; 6,45</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 6,73</t>
+          <t>4,45; 6,74</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>6,12; 8,78</t>
+          <t>6,21; 8,75</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>7,42; 10,04</t>
+          <t>7,52; 10,08</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>7,25; 11,31</t>
+          <t>9,83; 12,21</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>3,0; 4,32</t>
+          <t>3,08; 4,39</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>4,39; 5,95</t>
+          <t>4,38; 5,86</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>5,01; 6,52</t>
+          <t>5,06; 6,59</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>5,86; 8,27</t>
+          <t>7,52; 9,01</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,31%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,19%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,27%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1,53; 4,21</t>
+          <t>1,65; 4,15</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>1,4; 4,82</t>
+          <t>1,44; 5,04</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0,88; 3,47</t>
+          <t>0,91; 3,7</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>3,53; 7,53</t>
+          <t>3,72; 7,42</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 6,51</t>
+          <t>2,52; 6,37</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>2,3; 6,26</t>
+          <t>2,12; 6,1</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1,82; 5,1</t>
+          <t>1,86; 5,16</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>5,58; 9,29</t>
+          <t>5,51; 8,91</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,41; 4,75</t>
+          <t>2,41; 4,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,2; 4,65</t>
+          <t>2,18; 4,68</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>1,72; 3,81</t>
+          <t>1,68; 3,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>5,0; 7,72</t>
+          <t>5,07; 7,68</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>6,11%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>11,29%</t>
+          <t>12,23%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>9,26%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2,52; 3,74</t>
+          <t>2,54; 3,71</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>3,47; 4,89</t>
+          <t>3,4; 4,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2,72; 3,9</t>
+          <t>2,71; 4,02</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>4,3; 6,63</t>
+          <t>5,29; 7,02</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>6,72; 8,53</t>
+          <t>6,57; 8,42</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,35; 12,52</t>
+          <t>10,35; 12,49</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>9,08; 11,23</t>
+          <t>9,09; 11,26</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>9,22; 12,49</t>
+          <t>11,3; 13,11</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>4,91; 5,96</t>
+          <t>4,78; 5,92</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>7,16; 8,51</t>
+          <t>7,17; 8,53</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>6,22; 7,52</t>
+          <t>6,18; 7,44</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>7,43; 9,48</t>
+          <t>8,67; 9,87</t>
         </is>
       </c>
     </row>
@@ -1451,7 +1451,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>54712</t>
+          <t>57107</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1471,7 +1471,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>147236</t>
+          <t>163533</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1491,7 +1491,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>201949</t>
+          <t>220640</t>
         </is>
       </c>
     </row>
@@ -1504,62 +1504,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>41532; 69900</t>
+          <t>41594; 70644</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>49272; 83884</t>
+          <t>50936; 84639</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>28516; 53274</t>
+          <t>29271; 53226</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>43304; 68342</t>
+          <t>44815; 70781</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>127684; 172285</t>
+          <t>126221; 170981</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>226155; 284830</t>
+          <t>228856; 288663</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>144902; 194098</t>
+          <t>144697; 191787</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>131296; 162542</t>
+          <t>146079; 180466</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>178263; 232728</t>
+          <t>178441; 232674</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>290928; 362647</t>
+          <t>291403; 361327</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>180667; 236105</t>
+          <t>180832; 236716</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>180388; 222192</t>
+          <t>196525; 243625</t>
         </is>
       </c>
     </row>
@@ -1659,7 +1659,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>108979</t>
+          <t>120124</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1679,7 +1679,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>217897</t>
+          <t>239609</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -1699,7 +1699,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>326876</t>
+          <t>359733</t>
         </is>
       </c>
     </row>
@@ -1712,62 +1712,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>21222; 43688</t>
+          <t>22120; 43799</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>45181; 80643</t>
+          <t>44709; 79358</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>45005; 76946</t>
+          <t>46426; 77604</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>72752; 134134</t>
+          <t>100403; 143766</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>69719; 106828</t>
+          <t>70683; 106952</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>107364; 154026</t>
+          <t>109039; 153452</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>147513; 199711</t>
+          <t>149546; 200339</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>162228; 253074</t>
+          <t>213341; 265143</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>98436; 141785</t>
+          <t>101050; 143912</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>163197; 221172</t>
+          <t>162863; 218003</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>203621; 265070</t>
+          <t>205569; 268014</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>265300; 374527</t>
+          <t>330974; 396450</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>33676</t>
+          <t>37816</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1887,7 +1887,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>47404</t>
+          <t>52820</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -1907,7 +1907,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>81079</t>
+          <t>90636</t>
         </is>
       </c>
     </row>
@@ -1920,62 +1920,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>8446; 23222</t>
+          <t>9114; 22881</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>6757; 23213</t>
+          <t>6926; 24231</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4818; 18972</t>
+          <t>4975; 20231</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>22858; 48705</t>
+          <t>26483; 52787</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>13087; 30996</t>
+          <t>12001; 30334</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>10562; 28717</t>
+          <t>9708; 27969</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9986; 27992</t>
+          <t>10214; 28350</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36855; 61352</t>
+          <t>40513; 65446</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24763; 48784</t>
+          <t>24721; 50007</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>20710; 43656</t>
+          <t>20455; 44011</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18859; 41711</t>
+          <t>18452; 42436</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>65290; 100892</t>
+          <t>73407; 111036</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>197367</t>
+          <t>215047</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2095,7 +2095,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>412537</t>
+          <t>455962</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2115,7 +2115,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>609904</t>
+          <t>671009</t>
         </is>
       </c>
     </row>
@@ -2128,62 +2128,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>82672; 122507</t>
+          <t>83266; 121468</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>118636; 167214</t>
+          <t>116140; 166870</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>91881; 131811</t>
+          <t>91405; 135709</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>148591; 229004</t>
+          <t>186300; 247141</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>226997; 288276</t>
+          <t>222029; 284522</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>367564; 444633</t>
+          <t>367574; 443427</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>320816; 396560</t>
+          <t>321124; 397819</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>336824; 456287</t>
+          <t>421420; 488850</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>326547; 396959</t>
+          <t>318267; 393864</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>499446; 593168</t>
+          <t>499630; 594297</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>430016; 519891</t>
+          <t>427283; 514294</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>528253; 673333</t>
+          <t>628318; 715440</t>
         </is>
       </c>
     </row>
